--- a/Questions1.xlsx
+++ b/Questions1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\priya\Downloads\node.js\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F208B9B-002C-4A44-8EA6-C4B590A68234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F0635F-30EA-4B84-9F52-CBFA22805E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11775" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,8 +44,8 @@
     <t>We are deeply grateful to Vikas Jain (Indore) for bringing this idea to life and dedicating his time and knowledge to design most of the questions. Thank you so much, Vikasji. Jai Jinendra.</t>
   </si>
   <si>
-    <t>Jai Jinendra! Thank you for playing. We hope you enjoyed learning! Every answer is carefully verified, but if you find a mistake, please reach out. Simply quote the reference number shown in the top-right blue box when sending your comments so we can quickly update it for future players.
-जय जिनेंद्र! खेल खेलने के लिए आपका धन्यवाद। हमें उम्मीद है कि आपको इसके माध्यम से सीखने में आनंद आया होगा! हर उत्तर की जांच पूरी सावधानी से की गई है, लेकिन यदि आपको कोई गलती मिलती है, तो कृपया हमसे संपर्क करें। अपनी टिप्पणी भेजते समय ऊपरी-दाहिनी ओर (top-right) नीले बॉक्स में दिए गए संदर्भ नंबर (reference number) का उल्लेख ज़रूर करें, ताकि हम अन्य खिलाड़ियों के लिए इसे जल्द से जल्द सुधार सकें।</t>
+    <t>&lt;div&gt;Jai Jinendra! Thank you for playing. We hope you will enjoy learning! Every answer is carefully verified, but if you find any mistake, please reach out. Simply quote the reference number shown in the top-right blue box when sending your comments so we can quickly update it for future players.&lt;/div&gt;&lt;br&gt;
+&lt;div&gt;जय जिनेंद्र! खेल खेलने के लिए आपका धन्यवाद। हमें उम्मीद है कि आपको इसके माध्यम से सीखने में आनंद आयेगा! हर उत्तर की जांच पूरी सावधानी से की गई है, लेकिन यदि आपको कोई गलती मिलती है, तो कृपया हमसे संपर्क करें। अपनी टिप्पणी भेजते समय ऊपरी-दाहिनी ओर (top-right) नीले बॉक्स में दिए गए संदर्भ नंबर (reference number) का उल्लेख ज़रूर करें, ताकि हम अन्य खिलाड़ियों के लिए इसे जल्द से जल्द सुधार सकें।&lt;/div&gt;</t>
   </si>
 </sst>
 </file>

--- a/Questions1.xlsx
+++ b/Questions1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\priya\Downloads\node.js\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F0635F-30EA-4B84-9F52-CBFA22805E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{552C19BA-DBE0-4825-9D9E-74863921B6FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11775" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,10 @@
   </si>
   <si>
     <t>&lt;div&gt;Jai Jinendra! Thank you for playing. We hope you will enjoy learning! Every answer is carefully verified, but if you find any mistake, please reach out. Simply quote the reference number shown in the top-right blue box when sending your comments so we can quickly update it for future players.&lt;/div&gt;&lt;br&gt;
-&lt;div&gt;जय जिनेंद्र! खेल खेलने के लिए आपका धन्यवाद। हमें उम्मीद है कि आपको इसके माध्यम से सीखने में आनंद आयेगा! हर उत्तर की जांच पूरी सावधानी से की गई है, लेकिन यदि आपको कोई गलती मिलती है, तो कृपया हमसे संपर्क करें। अपनी टिप्पणी भेजते समय ऊपरी-दाहिनी ओर (top-right) नीले बॉक्स में दिए गए संदर्भ नंबर (reference number) का उल्लेख ज़रूर करें, ताकि हम अन्य खिलाड़ियों के लिए इसे जल्द से जल्द सुधार सकें।&lt;/div&gt;</t>
+&lt;br&gt;
+&lt;div&gt;जय जिनेंद्र! खेल खेलने के लिए आपका धन्यवाद। हमें उम्मीद है कि आपको इसके माध्यम से सीखने में आनंद आयेगा! हर उत्तर की जांच पूरी सावधानी से की गई है, लेकिन यदि आपको कोई गलती मिलती है, तो कृपया हमसे संपर्क करें। अपनी टिप्पणी भेजते समय ऊपरी-दाहिनी ओर (top-right) नीले बॉक्स में दिए गए संदर्भ नंबर (reference number) का उल्लेख ज़रूर करें, ताकि हम अन्य खिलाड़ियों के लिए इसे जल्द से जल्द सुधार सकें।&lt;/div&gt;
+&lt;br&gt;&lt;br&gt;
+Contact/ संपर्क: &lt;a href="https://forms.gle/deGsikyQ7eAQQVRPA" target="_blank"&gt;Click Here/ यहाँ क्लिक करें&lt;/a&gt;</t>
   </si>
 </sst>
 </file>
@@ -412,7 +415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" ht="105" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>

--- a/Questions1.xlsx
+++ b/Questions1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\priya\Downloads\node.js\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{552C19BA-DBE0-4825-9D9E-74863921B6FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{405451B2-3EDD-4043-94F3-DBD39E3071ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11775" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,10 +44,13 @@
     <t>We are deeply grateful to Vikas Jain (Indore) for bringing this idea to life and dedicating his time and knowledge to design most of the questions. Thank you so much, Vikasji. Jai Jinendra.</t>
   </si>
   <si>
-    <t>&lt;div&gt;Jai Jinendra! Thank you for playing. We hope you will enjoy learning! Every answer is carefully verified, but if you find any mistake, please reach out. Simply quote the reference number shown in the top-right blue box when sending your comments so we can quickly update it for future players.&lt;/div&gt;&lt;br&gt;
+    <t>&lt;div&gt;
+  Jai Jinendra! Thank you for playing. We hope you enjoy learning along the way! Every answer is carefully verified, but if you spot an error, have general feedback, or would like to suggest a new question or improvement, we’d love to hear from you. If your feedback is regarding an existing question, please quote the reference number shown in the top-right blue box so we can review and update it quickly.
+&lt;/div&gt;
+&lt;div&gt;
+  जय जिनेंद्र! खेलने के लिए आपका बहुत-बहुत धन्यवाद। हमें आशा है कि आपको सीखने में आनंद आ रहा होगा! प्रत्येक उत्तर की पूरी सावधानी से जाँच की गई है, फिर भी यदि आपको कोई त्रुटि मिलती है, आपके पास कोई सामान्य प्रतिक्रिया है, या आप किसी नए प्रश्न का सुझाव देना चाहते हैं, तो कृपया हमसे संपर्क करें। यदि आपकी प्रतिक्रिया किसी मौजूदा प्रश्न के बारे में है, तो कृपया ऊपरी-दाहिनी ओर (top-right) नीले बॉक्स में दिए गए संदर्भ नंबर (reference number) का उल्लेख ज़रूर करें, ताकि हम इसे जल्द से जल्द सुधार सकें।
+&lt;/div&gt;
 &lt;br&gt;
-&lt;div&gt;जय जिनेंद्र! खेल खेलने के लिए आपका धन्यवाद। हमें उम्मीद है कि आपको इसके माध्यम से सीखने में आनंद आयेगा! हर उत्तर की जांच पूरी सावधानी से की गई है, लेकिन यदि आपको कोई गलती मिलती है, तो कृपया हमसे संपर्क करें। अपनी टिप्पणी भेजते समय ऊपरी-दाहिनी ओर (top-right) नीले बॉक्स में दिए गए संदर्भ नंबर (reference number) का उल्लेख ज़रूर करें, ताकि हम अन्य खिलाड़ियों के लिए इसे जल्द से जल्द सुधार सकें।&lt;/div&gt;
-&lt;br&gt;&lt;br&gt;
 Contact/ संपर्क: &lt;a href="https://forms.gle/deGsikyQ7eAQQVRPA" target="_blank"&gt;Click Here/ यहाँ क्लिक करें&lt;/a&gt;</t>
   </si>
 </sst>
@@ -415,7 +418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="105" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" ht="165" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>

--- a/Questions1.xlsx
+++ b/Questions1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\priya\Downloads\node.js\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{405451B2-3EDD-4043-94F3-DBD39E3071ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AFC39B0-C2E1-4CF1-A70F-0A8B2C19F074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11775" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,11 +46,11 @@
   <si>
     <t>&lt;div&gt;
   Jai Jinendra! Thank you for playing. We hope you enjoy learning along the way! Every answer is carefully verified, but if you spot an error, have general feedback, or would like to suggest a new question or improvement, we’d love to hear from you. If your feedback is regarding an existing question, please quote the reference number shown in the top-right blue box so we can review and update it quickly.
-&lt;/div&gt;
+&lt;/div&gt;&lt;br&gt;
 &lt;div&gt;
   जय जिनेंद्र! खेलने के लिए आपका बहुत-बहुत धन्यवाद। हमें आशा है कि आपको सीखने में आनंद आ रहा होगा! प्रत्येक उत्तर की पूरी सावधानी से जाँच की गई है, फिर भी यदि आपको कोई त्रुटि मिलती है, आपके पास कोई सामान्य प्रतिक्रिया है, या आप किसी नए प्रश्न का सुझाव देना चाहते हैं, तो कृपया हमसे संपर्क करें। यदि आपकी प्रतिक्रिया किसी मौजूदा प्रश्न के बारे में है, तो कृपया ऊपरी-दाहिनी ओर (top-right) नीले बॉक्स में दिए गए संदर्भ नंबर (reference number) का उल्लेख ज़रूर करें, ताकि हम इसे जल्द से जल्द सुधार सकें।
 &lt;/div&gt;
-&lt;br&gt;
+&lt;br&gt;&lt;hr&gt;
 Contact/ संपर्क: &lt;a href="https://forms.gle/deGsikyQ7eAQQVRPA" target="_blank"&gt;Click Here/ यहाँ क्लिक करें&lt;/a&gt;</t>
   </si>
 </sst>
